--- a/Finalisation-concertation/ig/StructureDefinition-fr-uf-role.xlsx
+++ b/Finalisation-concertation/ig/StructureDefinition-fr-uf-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:36:59+00:00</t>
+    <t>2026-05-21T12:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Finalisation-concertation/ig/StructureDefinition-fr-uf-role.xlsx
+++ b/Finalisation-concertation/ig/StructureDefinition-fr-uf-role.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-uf-role</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-uf-role</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:38:31+00:00</t>
+    <t>2026-05-21T13:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -344,7 +344,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/fr-uf-role-code-for-prescription</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/fr-uf-role-code-for-prescription</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -686,7 +686,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.09765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.06640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
